--- a/outputs/LBE_Q1_2026_M1.xlsx
+++ b/outputs/LBE_Q1_2026_M1.xlsx
@@ -1238,7 +1238,7 @@
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>January sticks +13,991; -42,490 materializes on the open months. -100,251 in Q1 if the accrual holds at 100% of target; each 10 points of company multiplier is roughly USD 10.4k a quarter in G&amp;A alone.</t>
+          <t>January sticks +13,991; -42,490 materializes on the open months. Not an overspend.</t>
         </is>
       </c>
       <c r="I29" s="10" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>January sticks +148,153; -74,064 materializes on the open months. +64,900 a month while the roster holds; +129,800 Feb+Mar.</t>
+          <t>January sticks +148,153; -74,064 materializes on the open months. Loaded rate USD 17,051 against USD 19,322 planned = +88,574 (roster loaded average USD 193,505 against the plan's USD 214,000); heads 39 against....</t>
         </is>
       </c>
       <c r="I30" s="10" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>January sticks -221,052. -177,000 Feb+Mar if the reservation recurs; -88,500 Jan already booked.</t>
+          <t>January sticks -221,052. CoreWeave reserved H200 training capacity USD 88,500, moved out of cost of revenue by ADJ-2026-01-003; the 6050 envelope of USD 26,318 was never....</t>
         </is>
       </c>
       <c r="I31" s="10" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>January sticks +59,315. +64,900 a month while the roster holds; +129,800 Feb+Mar.</t>
+          <t>January sticks +59,315. Loaded rate USD 17,051 against USD 19,322 planned = +88,574 (roster loaded average USD 193,505 against the plan's USD 214,000); heads 39 against....</t>
         </is>
       </c>
       <c r="I32" s="10" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
-          <t>January sticks +46,139. +64,900 a month while the roster holds; +129,800 Feb+Mar.</t>
+          <t>January sticks +46,139. Loaded rate USD 17,051 against USD 19,322 planned = +88,574 (roster loaded average USD 193,505 against the plan's USD 214,000); heads 39 against....</t>
         </is>
       </c>
       <c r="I33" s="10" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>+71,084 materializes on the open months. Q1 favorable approx USD 255k.</t>
+          <t>+71,084 materializes on the open months. Loaded cost per head, not heads.</t>
         </is>
       </c>
       <c r="I34" s="10" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>+38,496 materializes on the open months. Q1 favorable approx USD 255k.</t>
+          <t>+38,496 materializes on the open months. Loaded cost per head, not heads.</t>
         </is>
       </c>
       <c r="I35" s="10" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>+41,327 materializes on the open months. Q1 favorable approx USD 255k.</t>
+          <t>+41,327 materializes on the open months. Loaded cost per head, not heads.</t>
         </is>
       </c>
       <c r="I36" s="10" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>+8,492 materializes on the open months. Q1 favorable approx USD 255k.</t>
+          <t>+8,492 materializes on the open months. Loaded cost per head, not heads.</t>
         </is>
       </c>
       <c r="I37" s="10" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>+30,486 materializes on the open months. Q1 favorable approx USD 255k.</t>
+          <t>+30,486 materializes on the open months. Loaded cost per head, not heads.</t>
         </is>
       </c>
       <c r="I38" s="10" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>+33,646 materializes on the open months. Q1 favorable approx USD 255k.</t>
+          <t>+33,646 materializes on the open months. Loaded cost per head, not heads.</t>
         </is>
       </c>
       <c r="I39" s="10" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>+40,569 materializes on the open months. Q1 favorable approx USD 255k.</t>
+          <t>+40,569 materializes on the open months. Loaded cost per head, not heads.</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>January sticks -4,361; -40,010 materializes on the open months. +29,912 in Q1 (Jan +36,559, Feb -3,324, Mar -3,324); nil for the full year.</t>
+          <t>January sticks -4,361; -40,010 materializes on the open months. Delaware franchise tax invoiced in full at USD 39,882 on 6 Jan and spread over the year it covers by ADJ-2026-01-010; the plan expensed the whole....</t>
         </is>
       </c>
       <c r="I41" s="10" t="inlineStr">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>-37,970 materializes on the open months. -23,106 in Q1 at the January rate; the account is -24,660 including Riviera Partners.</t>
+          <t>-37,970 materializes on the open months. The plan is the problem, not the month.</t>
         </is>
       </c>
       <c r="I42" s="10" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>January sticks -35,162; -25,627 materializes on the open months. -35,162 in Q1 (Jan -25,364, Feb -10,224, Mar +426), of which -19,400 is the non-recurring renewal accrual.</t>
+          <t>January sticks -35,162; -25,627 materializes on the open months. Two components.</t>
         </is>
       </c>
       <c r="I43" s="10" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
-          <t>-13,280 materializes on the open months. -100,251 in Q1 if the accrual holds at 100% of target; each 10 points of company multiplier is roughly USD 10.4k a quarter in G&amp;A alone.</t>
+          <t>-13,280 materializes on the open months. Not an overspend.</t>
         </is>
       </c>
       <c r="I44" s="10" t="inlineStr">
@@ -1884,7 +1884,7 @@
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>211200</v>
+        <v>242590.41</v>
       </c>
       <c r="D49" s="8" t="n">
         <v>0</v>
@@ -2211,7 +2211,7 @@
         </is>
       </c>
       <c r="C69" s="8" t="n">
-        <v>-47938.54</v>
+        <v>-48897.36</v>
       </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
@@ -2267,165 +2267,165 @@
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>6030 R&amp;D - contractors / Thoughtbolt Engineering LLC</t>
+          <t>4020 Professional services revenue / (customer billing)</t>
         </is>
       </c>
       <c r="C73" s="8" t="n">
-        <v>-17221.02</v>
+        <v>4565.35</v>
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
-          <t>Volume-driven. Invoiced hours USD 25,525.50 (in line with the December run rate of USD 24,310) plus a USD 16,200 accrual for January hours on TBE-0126 - the whole overrun is the accrual</t>
+          <t>Timing. Milestone delivery landed USD 4,565 ahead of the planned schedule on a line with a coefficient of variation of 0.503. Against the trailing 3-month average of USD 120,458 the month is down USD 23,892, which is calendar, not trend.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>4020 Professional services revenue / (customer billing)</t>
+          <t>7060 S&amp;M - software and tools / All other agreements (six vendors)</t>
         </is>
       </c>
       <c r="C74" s="8" t="n">
-        <v>4565.35</v>
+        <v>3684.07</v>
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
-          <t>Timing. Milestone delivery landed USD 4,565 ahead of the planned schedule on a line with a coefficient of variation of 0.503. Against the trailing 3-month average of USD 120,458 the month is down USD 23,892, which is calendar, not trend.</t>
+          <t>Timing. Every non-Gong agreement in 7060 is favorable by exactly 9.55 percent - Clearscope, HubSpot, Salesforce, Sprout Social, Webflow and ZoomInfo, plus Chorus and Lucid above. A single identical percentage across eight independent contracts is a release-convention artifact, not eight separate savings. It offsets most of the Gong uplift at the account level (7060 total unfavorable only USD 832 against a Gong uplift of USD 6,156), which is exactly how a real cost increase gets hidden in an account subtotal.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>7060 S&amp;M - software and tools / All other agreements (six vendors)</t>
+          <t>6030 R&amp;D - contractors / Thoughtbolt Engineering LLC</t>
         </is>
       </c>
       <c r="C75" s="8" t="n">
-        <v>3684.07</v>
+        <v>-1021.02</v>
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>Timing. Every non-Gong agreement in 7060 is favorable by exactly 9.55 percent - Clearscope, HubSpot, Salesforce, Sprout Social, Webflow and ZoomInfo, plus Chorus and Lucid above. A single identical percentage across eight independent contracts is a release-convention artifact, not eight separate savings. It offsets most of the Gong uplift at the account level (7060 total unfavorable only USD 832 against a Gong uplift of USD 6,156), which is exactly how a real cost increase gets hidden in an account subtotal.</t>
+          <t>Volume-driven. Invoiced hours USD 25,525.50 (in line with the December run rate of USD 24,310) plus a USD 16,200 accrual for January hours on TBE-0126 - the whole overrun is the accrual</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>8050 G&amp;A - software and tools / Okta, Inc.</t>
+          <t>7050 S&amp;M - events and conferences / Freeman, Goldcast, Informa</t>
         </is>
       </c>
       <c r="C76" s="8" t="n">
-        <v>3141.29</v>
+        <v>672</v>
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
-          <t>Accrual artifact. Not a saving. Every one of the eight prepaid-released G&amp;A subscriptions is favorable by exactly 40.97 percent - the release is 59.03 percent of contracted ACV/12 on all eight, to five decimal places. One common factor, so one common cause: the prepaid amortization schedule is releasing below the contracted rate. The agreement (SWA-0065) is a 12-month term at USD 92,000 with 0 percent uplift and the sole 8050 posting for this vendor is the prepaid release, so ACV/12 is the correct monthly charge. Licenses active 97 of 120. Under-release understates expense now and leaves a prepaid balance that will not extinguish at term end.</t>
+          <t>Timing. Calendar-driven, not a trend. The plan itself ramps across Q1 (Jan USD 8,400, Feb USD 11,760, Mar USD 26,880) because the named event calendar puts the Q1 event in March. Trailing three-month average of USD 21,467 is inflated by Q4-2025 events; the trend file flags the line bumpy (CoV 0.83) and says so. January is on the calendar and on plan.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>8050 G&amp;A - software and tools / Slack (Salesforce)</t>
+          <t>8050 G&amp;A - software and tools / Okta, Inc.</t>
         </is>
       </c>
       <c r="C77" s="8" t="n">
-        <v>2663.26</v>
+        <v>0</v>
       </c>
       <c r="H77" s="10" t="inlineStr">
         <is>
-          <t>Accrual artifact. Not a saving. Every one of the eight prepaid-released G&amp;A subscriptions is favorable by exactly 40.97 percent - the release is 59.03 percent of contracted ACV/12 on all eight, to five decimal places. One common factor, so one common cause: the prepaid amortization schedule is releasing below the contracted rate. The agreement (SWA-0069) is a 12-month term at USD 78,000 with 0 percent uplift and the sole 8050 posting for this vendor is the prepaid release, so ACV/12 is the correct monthly charge. Licenses active 143 of 180. Under-release understates expense now and leaves a prepaid balance that will not extinguish at term end.</t>
+          <t>Accrual artifact. Not a saving. Every one of the eight prepaid-released G&amp;A subscriptions is favorable by exactly 40.97 percent - the release is 59.03 percent of contracted ACV/12 on all eight, to five decimal places. One common factor, so one common cause: the prepaid amortization schedule is releasing below the contracted rate. The agreement (SWA-0065) is a 12-month term at USD 92,000 with 0 percent uplift and the sole 8050 posting for this vendor is the prepaid release, so ACV/12 is the correct monthly charge. Licenses active 97 of 120. Under-release understates expense now and leaves a prepaid balance that will not extinguish at term end.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>8050 G&amp;A - software and tools / CrowdStrike, Inc.</t>
+          <t>8050 G&amp;A - software and tools / Slack (Salesforce)</t>
         </is>
       </c>
       <c r="C78" s="8" t="n">
-        <v>2185.24</v>
+        <v>0</v>
       </c>
       <c r="H78" s="10" t="inlineStr">
         <is>
-          <t>Accrual artifact. Not a saving. Every one of the eight prepaid-released G&amp;A subscriptions is favorable by exactly 40.97 percent - the release is 59.03 percent of contracted ACV/12 on all eight, to five decimal places. One common factor, so one common cause: the prepaid amortization schedule is releasing below the contracted rate. The agreement (SWA-0067) is a 12-month term at USD 64,000 with 0 percent uplift and the sole 8050 posting for this vendor is the prepaid release, so ACV/12 is the correct monthly charge. Licenses active not seat-based. Under-release understates expense now and leaves a prepaid balance that will not extinguish at term end.</t>
+          <t>Accrual artifact. Not a saving. Every one of the eight prepaid-released G&amp;A subscriptions is favorable by exactly 40.97 percent - the release is 59.03 percent of contracted ACV/12 on all eight, to five decimal places. One common factor, so one common cause: the prepaid amortization schedule is releasing below the contracted rate. The agreement (SWA-0069) is a 12-month term at USD 78,000 with 0 percent uplift and the sole 8050 posting for this vendor is the prepaid release, so ACV/12 is the correct monthly charge. Licenses active 143 of 180. Under-release understates expense now and leaves a prepaid balance that will not extinguish at term end.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>8050 G&amp;A - software and tools / Vanta Inc.</t>
+          <t>8050 G&amp;A - software and tools / CrowdStrike, Inc.</t>
         </is>
       </c>
       <c r="C79" s="8" t="n">
-        <v>1297.49</v>
+        <v>0</v>
       </c>
       <c r="H79" s="10" t="inlineStr">
         <is>
-          <t>Accrual artifact. Not a saving. Every one of the eight prepaid-released G&amp;A subscriptions is favorable by exactly 40.97 percent - the release is 59.03 percent of contracted ACV/12 on all eight, to five decimal places. One common factor, so one common cause: the prepaid amortization schedule is releasing below the contracted rate. The agreement (SWA-0064) is a 12-month term at USD 38,000 with 0 percent uplift and the sole 8050 posting for this vendor is the prepaid release, so ACV/12 is the correct monthly charge. Licenses active not seat-based. Under-release understates expense now and leaves a prepaid balance that will not extinguish at term end.</t>
+          <t>Accrual artifact. Not a saving. Every one of the eight prepaid-released G&amp;A subscriptions is favorable by exactly 40.97 percent - the release is 59.03 percent of contracted ACV/12 on all eight, to five decimal places. One common factor, so one common cause: the prepaid amortization schedule is releasing below the contracted rate. The agreement (SWA-0067) is a 12-month term at USD 64,000 with 0 percent uplift and the sole 8050 posting for this vendor is the prepaid release, so ACV/12 is the correct monthly charge. Licenses active not seat-based. Under-release understates expense now and leaves a prepaid balance that will not extinguish at term end.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>8050 G&amp;A - software and tools / Zoom Communications</t>
+          <t>8050 G&amp;A - software and tools / Vanta Inc.</t>
         </is>
       </c>
       <c r="C80" s="8" t="n">
-        <v>1160.91</v>
+        <v>0</v>
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
-          <t>Accrual artifact. Not a saving. Every one of the eight prepaid-released G&amp;A subscriptions is favorable by exactly 40.97 percent - the release is 59.03 percent of contracted ACV/12 on all eight, to five decimal places. One common factor, so one common cause: the prepaid amortization schedule is releasing below the contracted rate. The agreement (SWA-0071) is a 12-month term at USD 34,000 with 0 percent uplift and the sole 8050 posting for this vendor is the prepaid release, so ACV/12 is the correct monthly charge. Licenses active 31 of 45. Under-release understates expense now and leaves a prepaid balance that will not extinguish at term end.</t>
+          <t>Accrual artifact. Not a saving. Every one of the eight prepaid-released G&amp;A subscriptions is favorable by exactly 40.97 percent - the release is 59.03 percent of contracted ACV/12 on all eight, to five decimal places. One common factor, so one common cause: the prepaid amortization schedule is releasing below the contracted rate. The agreement (SWA-0064) is a 12-month term at USD 38,000 with 0 percent uplift and the sole 8050 posting for this vendor is the prepaid release, so ACV/12 is the correct monthly charge. Licenses active not seat-based. Under-release understates expense now and leaves a prepaid balance that will not extinguish at term end.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>8050 G&amp;A - software and tools / Notion Labs, Inc.</t>
+          <t>8050 G&amp;A - software and tools / Zoom Communications</t>
         </is>
       </c>
       <c r="C81" s="8" t="n">
-        <v>1058.47</v>
+        <v>0</v>
       </c>
       <c r="H81" s="10" t="inlineStr">
         <is>
-          <t>Accrual artifact. Not a saving. Every one of the eight prepaid-released G&amp;A subscriptions is favorable by exactly 40.97 percent - the release is 59.03 percent of contracted ACV/12 on all eight, to five decimal places. One common factor, so one common cause: the prepaid amortization schedule is releasing below the contracted rate. The agreement (SWA-0068) is a 12-month term at USD 31,000 with 0 percent uplift and the sole 8050 posting for this vendor is the prepaid release, so ACV/12 is the correct monthly charge. Licenses active 51 of 60. Under-release understates expense now and leaves a prepaid balance that will not extinguish at term end.</t>
+          <t>Accrual artifact. Not a saving. Every one of the eight prepaid-released G&amp;A subscriptions is favorable by exactly 40.97 percent - the release is 59.03 percent of contracted ACV/12 on all eight, to five decimal places. One common factor, so one common cause: the prepaid amortization schedule is releasing below the contracted rate. The agreement (SWA-0071) is a 12-month term at USD 34,000 with 0 percent uplift and the sole 8050 posting for this vendor is the prepaid release, so ACV/12 is the correct monthly charge. Licenses active 31 of 45. Under-release understates expense now and leaves a prepaid balance that will not extinguish at term end.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>8050 G&amp;A - software and tools / 1Password (AgileBits)</t>
+          <t>8050 G&amp;A - software and tools / Notion Labs, Inc.</t>
         </is>
       </c>
       <c r="C82" s="8" t="n">
-        <v>717.03</v>
+        <v>0</v>
       </c>
       <c r="H82" s="10" t="inlineStr">
         <is>
-          <t>Accrual artifact. Not a saving. Every one of the eight prepaid-released G&amp;A subscriptions is favorable by exactly 40.97 percent - the release is 59.03 percent of contracted ACV/12 on all eight, to five decimal places. One common factor, so one common cause: the prepaid amortization schedule is releasing below the contracted rate. The agreement (SWA-0066) is a 12-month term at USD 21,000 with 0 percent uplift and the sole 8050 posting for this vendor is the prepaid release, so ACV/12 is the correct monthly charge. Licenses active not seat-based. Under-release understates expense now and leaves a prepaid balance that will not extinguish at term end.</t>
+          <t>Accrual artifact. Not a saving. Every one of the eight prepaid-released G&amp;A subscriptions is favorable by exactly 40.97 percent - the release is 59.03 percent of contracted ACV/12 on all eight, to five decimal places. One common factor, so one common cause: the prepaid amortization schedule is releasing below the contracted rate. The agreement (SWA-0068) is a 12-month term at USD 31,000 with 0 percent uplift and the sole 8050 posting for this vendor is the prepaid release, so ACV/12 is the correct monthly charge. Licenses active 51 of 60. Under-release understates expense now and leaves a prepaid balance that will not extinguish at term end.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>7050 S&amp;M - events and conferences / Freeman, Goldcast, Informa</t>
+          <t>8050 G&amp;A - software and tools / 1Password (AgileBits)</t>
         </is>
       </c>
       <c r="C83" s="8" t="n">
-        <v>672</v>
+        <v>0</v>
       </c>
       <c r="H83" s="10" t="inlineStr">
         <is>
-          <t>Timing. Calendar-driven, not a trend. The plan itself ramps across Q1 (Jan USD 8,400, Feb USD 11,760, Mar USD 26,880) because the named event calendar puts the Q1 event in March. Trailing three-month average of USD 21,467 is inflated by Q4-2025 events; the trend file flags the line bumpy (CoV 0.83) and says so. January is on the calendar and on plan.</t>
+          <t>Accrual artifact. Not a saving. Every one of the eight prepaid-released G&amp;A subscriptions is favorable by exactly 40.97 percent - the release is 59.03 percent of contracted ACV/12 on all eight, to five decimal places. One common factor, so one common cause: the prepaid amortization schedule is releasing below the contracted rate. The agreement (SWA-0066) is a 12-month term at USD 21,000 with 0 percent uplift and the sole 8050 posting for this vendor is the prepaid release, so ACV/12 is the correct monthly charge. Licenses active not seat-based. Under-release understates expense now and leaves a prepaid balance that will not extinguish at term end.</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
         </is>
       </c>
       <c r="C84" s="8" t="n">
-        <v>614.6</v>
+        <v>0</v>
       </c>
       <c r="H84" s="10" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         </is>
       </c>
       <c r="D55" s="8" t="n">
-        <v>-70000</v>
+        <v>-83337.82000000001</v>
       </c>
       <c r="E55" s="8" t="n">
         <v>-84180.67</v>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="I80" s="10" t="inlineStr">
         <is>
-          <t>-74,064 materializes on the open months. -58,533 in Q1 if OI-02 is booked in February (Jan catch-up plus Feb and Mar at -19,511); a further -130,486 is a prior-period item outside Q1.</t>
+          <t>-74,064 materializes on the open months. USD 19,510.99 of the January capitalization is ARC-IUS-004 Model evaluation harness, carried at Preliminary project stage since June 2025 - not....</t>
         </is>
       </c>
       <c r="J80" s="7" t="inlineStr">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="I82" s="10" t="inlineStr">
         <is>
-          <t>+255,000 materializes on the open months. Q1 favorable approx USD 255k.</t>
+          <t>+255,000 materializes on the open months. Loaded cost per head, not heads.</t>
         </is>
       </c>
       <c r="J82" s="7" t="inlineStr">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="I83" s="10" t="inlineStr">
         <is>
-          <t>+44,000 materializes on the open months. Q1 favorable approx USD 44k, tracking 7000.</t>
+          <t>+44,000 materializes on the open months. Employer burden at 21.2 percent moving with the same base as 7000.</t>
         </is>
       </c>
       <c r="J83" s="7" t="inlineStr">
@@ -6270,7 +6270,7 @@
       </c>
       <c r="I86" s="10" t="inlineStr">
         <is>
-          <t>-14,000 materializes on the open months. Q1 unfavorable approx USD 14k if the 6 percent overspend holds.</t>
+          <t>-14,000 materializes on the open months. Pure media, no agency or event content in this account.</t>
         </is>
       </c>
       <c r="J86" s="7" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="I88" s="10" t="inlineStr">
         <is>
-          <t>-18,500 materializes on the open months. Q1 unfavorable approx USD 18.5k at the current release rate; approx USD 13.5k if the prepaid release is corrected to USD 12,333.33 a month.</t>
+          <t>-18,500 materializes on the open months. Auto-renewal uplift, not consumption.</t>
         </is>
       </c>
       <c r="J88" s="7" t="inlineStr">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="I89" s="10" t="inlineStr">
         <is>
-          <t>-2,400 materializes on the open months. Q1 unfavorable approx USD 2.4k.</t>
+          <t>-2,400 materializes on the open months. Benchmark is budget per head x budgeted headcount, so it splits two ways.</t>
         </is>
       </c>
       <c r="J89" s="7" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="I92" s="10" t="inlineStr">
         <is>
-          <t>-100,251 materializes on the open months. -100,251 in Q1 if the accrual holds at 100% of target; each 10 points of company multiplier is roughly USD 10.4k a quarter in G&amp;A alone.</t>
+          <t>-100,251 materializes on the open months. Not an overspend.</t>
         </is>
       </c>
       <c r="J92" s="7" t="inlineStr">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="I93" s="10" t="inlineStr">
         <is>
-          <t>-16,492 materializes on the open months. -16,492 in Q1.</t>
+          <t>-16,492 materializes on the open months. The same cause as 8000, one account down.</t>
         </is>
       </c>
       <c r="J93" s="7" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="I95" s="10" t="inlineStr">
         <is>
-          <t>-6,549 materializes on the open months. -6,549 in Q1 (Jan -2,478, Feb -4,248, Mar +177).</t>
+          <t>-6,549 materializes on the open months. A single commercial contracting invoice, 23 percent above a plan struck as December run rate x 1.2.</t>
         </is>
       </c>
       <c r="J95" s="7" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="I96" s="10" t="inlineStr">
         <is>
-          <t>-18,079 materializes on the open months. -18,079 in Q1 (Jan -2,916, Feb and Mar -15,163 at 9 percent on the planned fieldwork base).</t>
+          <t>-18,079 materializes on the open months. January is not the surprise and should not be reported as one - the fieldwork spike is in the calendar (FY2025 audit fieldwork completes 31 March)....</t>
         </is>
       </c>
       <c r="J96" s="7" t="inlineStr">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="I101" s="10" t="inlineStr">
         <is>
-          <t>+5,100 materializes on the open months. +5,100 in Q1 if the book and aging profile hold.</t>
+          <t>+5,100 materializes on the open months. The provision is the CECL aging matrix applied to the actual receivables book; the plan applied the same matrix to a planned book.</t>
         </is>
       </c>
       <c r="J101" s="7" t="inlineStr">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="I103" s="10" t="inlineStr">
         <is>
-          <t>-23,106 materializes on the open months. -23,106 in Q1 at the January rate; the account is -24,660 including Riviera Partners.</t>
+          <t>-23,106 materializes on the open months. The plan is the problem, not the month.</t>
         </is>
       </c>
       <c r="J103" s="7" t="inlineStr">
@@ -7124,11 +7124,11 @@
         </is>
       </c>
       <c r="D107" s="8" t="n">
-        <v>-70400</v>
+        <v>-80844.37</v>
       </c>
       <c r="E107" s="8" t="n"/>
       <c r="F107" s="8" t="n">
-        <v>-70400</v>
+        <v>-80844.37</v>
       </c>
       <c r="G107" s="8">
         <f>F107-D107</f>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="I132" s="10" t="inlineStr">
         <is>
-          <t>-74,064 materializes on the open months. -58,533 in Q1 if OI-02 is booked in February (Jan catch-up plus Feb and Mar at -19,511); a further -130,486 is a prior-period item outside Q1.</t>
+          <t>-74,064 materializes on the open months. USD 19,510.99 of the January capitalization is ARC-IUS-004 Model evaluation harness, carried at Preliminary project stage since June 2025 - not....</t>
         </is>
       </c>
       <c r="J132" s="7" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="I134" s="10" t="inlineStr">
         <is>
-          <t>+255,000 materializes on the open months. Q1 favorable approx USD 255k.</t>
+          <t>+255,000 materializes on the open months. Loaded cost per head, not heads.</t>
         </is>
       </c>
       <c r="J134" s="7" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="I135" s="10" t="inlineStr">
         <is>
-          <t>+44,000 materializes on the open months. Q1 favorable approx USD 44k, tracking 7000.</t>
+          <t>+44,000 materializes on the open months. Employer burden at 21.2 percent moving with the same base as 7000.</t>
         </is>
       </c>
       <c r="J135" s="7" t="inlineStr">
@@ -8442,7 +8442,7 @@
       </c>
       <c r="I138" s="10" t="inlineStr">
         <is>
-          <t>-14,000 materializes on the open months. Q1 unfavorable approx USD 14k if the 6 percent overspend holds.</t>
+          <t>-14,000 materializes on the open months. Pure media, no agency or event content in this account.</t>
         </is>
       </c>
       <c r="J138" s="7" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="I140" s="10" t="inlineStr">
         <is>
-          <t>-18,500 materializes on the open months. Q1 unfavorable approx USD 18.5k at the current release rate; approx USD 13.5k if the prepaid release is corrected to USD 12,333.33 a month.</t>
+          <t>-18,500 materializes on the open months. Auto-renewal uplift, not consumption.</t>
         </is>
       </c>
       <c r="J140" s="7" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="I141" s="10" t="inlineStr">
         <is>
-          <t>-2,400 materializes on the open months. Q1 unfavorable approx USD 2.4k.</t>
+          <t>-2,400 materializes on the open months. Benchmark is budget per head x budgeted headcount, so it splits two ways.</t>
         </is>
       </c>
       <c r="J141" s="7" t="inlineStr">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="I144" s="10" t="inlineStr">
         <is>
-          <t>-100,251 materializes on the open months. -100,251 in Q1 if the accrual holds at 100% of target; each 10 points of company multiplier is roughly USD 10.4k a quarter in G&amp;A alone.</t>
+          <t>-100,251 materializes on the open months. Not an overspend.</t>
         </is>
       </c>
       <c r="J144" s="7" t="inlineStr">
@@ -8739,7 +8739,7 @@
       </c>
       <c r="I145" s="10" t="inlineStr">
         <is>
-          <t>-16,492 materializes on the open months. -16,492 in Q1.</t>
+          <t>-16,492 materializes on the open months. The same cause as 8000, one account down.</t>
         </is>
       </c>
       <c r="J145" s="7" t="inlineStr">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="I147" s="10" t="inlineStr">
         <is>
-          <t>-6,549 materializes on the open months. -6,549 in Q1 (Jan -2,478, Feb -4,248, Mar +177).</t>
+          <t>-6,549 materializes on the open months. A single commercial contracting invoice, 23 percent above a plan struck as December run rate x 1.2.</t>
         </is>
       </c>
       <c r="J147" s="7" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="I148" s="10" t="inlineStr">
         <is>
-          <t>-18,079 materializes on the open months. -18,079 in Q1 (Jan -2,916, Feb and Mar -15,163 at 9 percent on the planned fieldwork base).</t>
+          <t>-18,079 materializes on the open months. January is not the surprise and should not be reported as one - the fieldwork spike is in the calendar (FY2025 audit fieldwork completes 31 March)....</t>
         </is>
       </c>
       <c r="J148" s="7" t="inlineStr">
@@ -9067,7 +9067,7 @@
       </c>
       <c r="I153" s="10" t="inlineStr">
         <is>
-          <t>+5,100 materializes on the open months. +5,100 in Q1 if the book and aging profile hold.</t>
+          <t>+5,100 materializes on the open months. The provision is the CECL aging matrix applied to the actual receivables book; the plan applied the same matrix to a planned book.</t>
         </is>
       </c>
       <c r="J153" s="7" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="I155" s="10" t="inlineStr">
         <is>
-          <t>-23,106 materializes on the open months. -23,106 in Q1 at the January rate; the account is -24,660 including Riviera Partners.</t>
+          <t>-23,106 materializes on the open months. The plan is the problem, not the month.</t>
         </is>
       </c>
       <c r="J155" s="7" t="inlineStr">
@@ -9296,11 +9296,11 @@
         </is>
       </c>
       <c r="D159" s="8" t="n">
-        <v>-70800</v>
+        <v>-78408.22</v>
       </c>
       <c r="E159" s="8" t="n"/>
       <c r="F159" s="8" t="n">
-        <v>-70800</v>
+        <v>-78408.22</v>
       </c>
       <c r="G159" s="8">
         <f>F159-D159</f>
